--- a/borchestra_achivments.xlsx
+++ b/borchestra_achivments.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,284 +436,284 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Atlas_Unlock_Achievement</t>
+          <t>EP_Intijar_BossBeat_ACH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Burdened</t>
+          <t>The Highbrow</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Unlock Atlas.</t>
+          <t>Murder Intijar.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Atlas_Witness_ACH</t>
+          <t>EP_Unicorn_BossBeat_ACH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chalcanthite</t>
+          <t>The Folly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Unlocked a new item.</t>
+          <t>Slay the Malformed Unicorn.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Atlas_Divine_ACH</t>
+          <t>EP_Squid_BossBeat_ACH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>First Pebble</t>
+          <t>The Loathsome</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Unlocked a new item.</t>
+          <t>Slay the Depression Squid.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Atlas_Abstraction_ACH</t>
+          <t>EP_Doula_BossBeat_ACH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Golden Pickaxe</t>
+          <t>The Abstraction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Unlocked a new item.</t>
+          <t>Abandon the Doula.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Atlas_Inevitable_ACH</t>
+          <t>EP_Kekapex_BossBeat_ACH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Candy Stones</t>
+          <t>The Early Bird Gets the Worm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Unlocked a new item.</t>
+          <t>Uproot the Kekapex.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Biersal_Witness_ACH</t>
+          <t>EP_Cherubim_BossBeat_ACH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Irish Car Bomb</t>
+          <t>Ezekiel 10:14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Unlocked a new item.</t>
+          <t>Desecrate the Cherubim.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Biersal_Divine_ACH</t>
+          <t>EP_Opisthotonus_BossBeat_ACH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Corpse Reviver</t>
+          <t>Thee I invoke, the Bornless one</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Unlocked a new item.</t>
+          <t>Exorcise the Opisthotonus.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biersal_Abstraction_ACH</t>
+          <t>EP_Fountain_BossBeat_ACH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Off-Brandy</t>
+          <t>Mud Feaster</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Unlocked a new item.</t>
+          <t>Drink the Fountain of Youth.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Biersal_Inevitable_ACH</t>
+          <t>EP_Highness_BossBeat_ACH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Whiskey Stones</t>
+          <t>He Wasn't Really Trying You Know...</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Unlocked a new item.</t>
+          <t>Flip the bird on the Heinous Highness.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dahlia_Unlock_Achievement</t>
+          <t>EP_Sachiel_BossBeat_ACH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Commander</t>
+          <t>How Many Times do We Have to Teach You this Lesson, Old Man?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Unlock Dahlia.</t>
+          <t>Ransack Sachiel.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dahlia_Witness_ACH</t>
+          <t>EP_AllBosses_BossBeat_ACH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sergal Spear</t>
+          <t>Lord Butcherer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Unlocked a new item.</t>
+          <t>Defeat all Bosses and Minibosses in the Enemy pack.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dahlia_Divine_ACH</t>
+          <t>EP_IntijarComedy_ACH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sharktooth Necklace</t>
+          <t>Ahead of Yourself</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Unlocked a new item.</t>
+          <t>Witness Intijar attempt to perform Brainstorm with no rocks present.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dahlia_Abstraction_ACH</t>
+          <t>EP_Gizo_Skinned_ACH</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ball Of Bandages</t>
+          <t>Mom says it's my turn</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Unlocked a new item.</t>
+          <t>Witness a Gizo skin a clothed Gizo.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dahlia_Inevitable_ACH</t>
+          <t>EP_UnicornComedy_ACH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Obsidian Blade</t>
+          <t>Six Feet Under</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Unlocked a new item.</t>
+          <t>Beat the Malformed Unicorn without damaging the Human Elemental.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Derek_Unlock_Achievement</t>
+          <t>EP_Boyle_Abstraction_ACH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Bulwark</t>
+          <t>Frying Pan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Unlock Derek.</t>
+          <t>Unlocked a new item.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Fel_Unlock_Achievement</t>
+          <t>EP_Fennec_Abstraction_ACH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Funky</t>
+          <t>Caged Beast</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Unlock Fel.</t>
+          <t>Unlocked a new item.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Fel_Witness_ACH</t>
+          <t>EP_Mordrake_Abstraction_ACH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nap Sack</t>
+          <t>Clonion</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -725,12 +725,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fel_Divine_ACH</t>
+          <t>EP_Griffin_Abstraction_ACH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Plastic Bag</t>
+          <t>Decapitated Rooster</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -742,12 +742,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Fel_Abstraction_ACH</t>
+          <t>EP_Splig_Abstraction_ACH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Anarchy Staff</t>
+          <t>Scalpel</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -759,12 +759,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Fel_Inevitable_ACH</t>
+          <t>EP_Agon_Abstraction_ACH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Necromancing Stone</t>
+          <t>Candle of Life</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -776,29 +776,29 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Gourd_Unlock_Achievement</t>
+          <t>EP_Hans_Abstraction_ACH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Blighted</t>
+          <t>Light Switch</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Unlock Gourd.</t>
+          <t>Unlocked a new item.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Gourd_Witness_ACH</t>
+          <t>EP_Leviat_Abstraction_ACH</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Crab Claw</t>
+          <t>Transference</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -810,12 +810,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gourd_Divine_ACH</t>
+          <t>EP_SmokeStacks_Abstraction_ACH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Inscissors</t>
+          <t>Abstruse Relic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -827,12 +827,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gourd_Abstraction_ACH</t>
+          <t>EP_Cranes_Abstraction_ACH</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Neural Worm</t>
+          <t>Discarded Cross</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -844,12 +844,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Gourd_Inevitable_ACH</t>
+          <t>EP_Thype_Abstraction_ACH</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Embalming Fluid</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -861,12 +861,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GreasyDerek_Witness_ACH</t>
+          <t>EP_Mung_Abstraction_ACH</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Little Knight</t>
+          <t>Ceramic Armor</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -878,12 +878,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GreasyDerek_Divine_ACH</t>
+          <t>EP_Kleiver_Abstraction_ACH</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tower Shield</t>
+          <t>Bleeding Ears</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GreasyDerek_Abstraction_ACH</t>
+          <t>EP_Burnout_Abstraction_ACH</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Log Suit</t>
+          <t>Your Fault</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -912,12 +912,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GreasyDerek_Inevitable_ACH</t>
+          <t>EP_Anton_Abstraction_ACH</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mohs Scale</t>
+          <t>Happy Pills</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -929,29 +929,29 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Oaths_Unlock_Achievement</t>
+          <t>EP_Arnold_Abstraction_ACH</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Beholder</t>
+          <t>Vermin</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Unlock Oaths.</t>
+          <t>Unlocked a new item.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Oaths_Witness_ACH</t>
+          <t>EP_LongLiver_Abstraction_ACH</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Love Letter</t>
+          <t>Bloody Valve</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -963,12 +963,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Oaths_Divine_ACH</t>
+          <t>EP_Rags_Abstraction_ACH</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Second Glass Eye</t>
+          <t>Copper Dagger</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -980,12 +980,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Oaths_Abstraction_ACH</t>
+          <t>EP_Pearl_Abstraction_ACH</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Glistening Goblet</t>
+          <t>Dead Canary</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Oaths_Inevitable_ACH</t>
+          <t>EP_Dimitri_CH_Abstraction_ACH</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Apache Tears</t>
+          <t>Burnt Letter</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1014,29 +1014,29 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Quarell_Unlock_Achievement</t>
+          <t>EP_Clive_CH_Abstraction_ACH</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Employee</t>
+          <t>Loose Scarf</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Unlock Quarell.</t>
+          <t>Unlocked a new item.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Quarell_Witness_ACH</t>
+          <t>EP_Bimini_CH_Abstraction_ACH</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Panic Button</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1048,12 +1048,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Quarell_Divine_ACH</t>
+          <t>EP_Gospel_CH_Abstraction_ACH</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sticky Note</t>
+          <t>Talia's Severed Head</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1065,374 +1065,104 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Quarell_Abstraction_ACH</t>
+          <t>EP_Mastery_ACH</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sweat-Powered Megamachine</t>
+          <t>Time Un-well Spent</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Unlocked a new item.</t>
+          <t>Achieve every Non-Abstraction achievement in the Enemy Pack.
+Tairbaz and Peep think you are pretty cool :)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Quarell_Inevitable_ACH</t>
+          <t>EP_Doula_Tragedy_ACH</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Dusty Keyboard</t>
+          <t>Animal Cruelty</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Unlocked a new item.</t>
+          <t>In an encounter with the Abstraction,
+Let the Doula grow to 10+ Multi-Attack</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RedRager_Unlock_Achievement</t>
+          <t>EP_Mimic_ACH</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>THE RAGER!!</t>
+          <t>Whoops!</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UNLOCK THE REDRAGER!!</t>
+          <t>Encounter a Sandbank or a Roadie.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Red_Rager_Witness_ACH</t>
+          <t>EP_SquidTragedy_ACH</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Liquid Hate</t>
+          <t>Punchline</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Unlocked a new item.</t>
+          <t>Witness the Depression Squid.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Red_Rager_Divine_ACH</t>
+          <t>EP_SachielTragedy_ACH</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Rageberry</t>
+          <t>Deal Gone Wrong</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Unlocked a new item.</t>
+          <t>Witness a mysterious stranger attempt to Fool-nap one of your fools.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Red_Rager_Abstraction_ACH</t>
+          <t>EP_Goblin_ACH</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Viper Venom</t>
+          <t>Punk'd</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Unlocked a new item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Red_Rager_Inevitable_ACH</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Rose-Tinted Glasses</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Unlocked a new item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Stain_Unlock_Achievement</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>The Awful</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Unlock Stain.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Stain_Witness_ACH</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Heart of Pyrite</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Unlocked a new item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Stain_Divine_ACH</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Amniotic Fluids</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Unlocked a new item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Stain_Abstraction_ACH</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Living Roadkill</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Unlocked a new item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Stain_Inevitable_ACH</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Biological Clock</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Unlocked a new item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Swell_Unlock_Achievement</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>The Horseman</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Unlock Swell.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Swell_Witness_ACH</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>ManifestationOfWar</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Unlocked a new item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Swell_Divine_ACH</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Rubber Mask</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Unlocked a new item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Swell_Abstraction_ACH</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>The Tick</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Unlocked a new item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Swell_Inevitable_ACH</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Toxic Waste</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Unlocked a new item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Whale_Unlock_Achievement</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>The Jaded</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Unlock Whale.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Whale_Witness_ACH</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Adverse Action Notice</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Unlocked a new item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Whale_Divine_ACH</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Faustian Contract</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Unlocked a new item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Whale_Abstraction_ACH</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Lotto Ticket</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Unlocked a new item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Whale_Inevitable_ACH</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Cement Shoes</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Unlocked a new item.</t>
+          <t>Become a victim to a horrible joke.</t>
         </is>
       </c>
     </row>
